--- a/data/japan_stock_dividend_db.xlsx
+++ b/data/japan_stock_dividend_db.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yabukikatsumi/Desktop/japan_stock_analysis/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{955FA8EA-DE67-BB4A-90ED-76E769FA25DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1380634-5B40-3B43-8864-9DFD3D19C6F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17220" xr2:uid="{B275AEFC-8BB2-B547-9029-F0A53A304833}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
   <si>
     <t>ナガセ</t>
     <phoneticPr fontId="1"/>
@@ -211,6 +211,20 @@
   </si>
   <si>
     <t>https://finance.yahoo.co.jp/quote/9733.T</t>
+  </si>
+  <si>
+    <t>BuffettCodeURL</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.buffett-code.com/company/9733/</t>
+  </si>
+  <si>
+    <t>IRBANKURL</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://irbank.net/E04824/results</t>
   </si>
 </sst>
 </file>
@@ -589,15 +603,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2E652AF-CEC1-9E49-9807-367A9602B169}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="31">
+    <row r="1" spans="1:7" ht="31">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -613,8 +629,14 @@
       <c r="E1" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>9733</v>
       </c>
@@ -629,6 +651,12 @@
       </c>
       <c r="E2" t="s">
         <v>25</v>
+      </c>
+      <c r="F2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
